--- a/data/generation_logs.xlsx
+++ b/data/generation_logs.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-03-16T12:26:55.827Z</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-03-16T12:27:03.582Z</v>
+      </c>
+      <c r="B4">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-03-16T12:27:06.180Z</v>
+      </c>
+      <c r="B5">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-03-16T12:27:07.770Z</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-03-16T12:27:08.659Z</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-03-16T12:36:19.702Z</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/generation_logs.xlsx
+++ b/data/generation_logs.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,6 +415,9 @@
       <c r="E1" t="str">
         <v>failed</v>
       </c>
+      <c r="F1" t="str">
+        <v>fallbackUsed</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +435,9 @@
       <c r="E2">
         <v>0</v>
       </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -449,6 +455,9 @@
       <c r="E3">
         <v>0</v>
       </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -466,6 +475,9 @@
       <c r="E4">
         <v>0</v>
       </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -483,6 +495,9 @@
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -500,6 +515,9 @@
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -517,6 +535,9 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -534,10 +555,633 @@
       <c r="E8">
         <v>0</v>
       </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-03-16T12:46:05.851Z</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-03-16T12:46:23.248Z</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-03-16T12:53:11.670Z</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-03-16T12:53:18.968Z</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-03-16T12:56:54.373Z</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-03-16T12:57:05.827Z</v>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-03-16T13:01:33.999Z</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-03-16T13:05:16.240Z</v>
+      </c>
+      <c r="B16">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-03-16T13:05:34.162Z</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-03-16T13:10:37.760Z</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-03-16T13:10:42.593Z</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-03-16T13:10:44.721Z</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-03-16T13:10:47.641Z</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-03-16T13:10:50.515Z</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-03-16T13:10:53.712Z</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-03-16T13:10:55.995Z</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-03-16T13:11:13.842Z</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-03-16T13:22:45.640Z</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-03-16T13:22:56.913Z</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-03-16T13:59:50.081Z</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-03-16T14:00:52.658Z</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-03-16T14:02:42.622Z</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-03-16T14:16:35.494Z</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-03-16T14:22:21.846Z</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-03-16T14:34:47.223Z</v>
+      </c>
+      <c r="B33">
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>20</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-03-16T14:35:09.711Z</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>20</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-03-16T14:35:33.633Z</v>
+      </c>
+      <c r="B35">
+        <v>17</v>
+      </c>
+      <c r="C35">
+        <v>17</v>
+      </c>
+      <c r="D35">
+        <v>17</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-03-16T15:06:09.054Z</v>
+      </c>
+      <c r="B36">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>17</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-03-16T15:06:19.227Z</v>
+      </c>
+      <c r="B37">
+        <v>16</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>16</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-03-16T15:06:38.394Z</v>
+      </c>
+      <c r="B38">
+        <v>17</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>17</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-03-16T15:06:48.665Z</v>
+      </c>
+      <c r="B39">
+        <v>17</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>17</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/generation_logs.xlsx
+++ b/data/generation_logs.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1179,9 +1179,169 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-03-20T06:16:52.216Z</v>
+      </c>
+      <c r="B40">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>20</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-03-20T06:17:06.886Z</v>
+      </c>
+      <c r="B41">
+        <v>20</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-03-20T06:19:32.403Z</v>
+      </c>
+      <c r="B42">
+        <v>17</v>
+      </c>
+      <c r="C42">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>17</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-03-20T06:26:05.255Z</v>
+      </c>
+      <c r="B43">
+        <v>20</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-03-20T06:26:10.897Z</v>
+      </c>
+      <c r="B44">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>20</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-03-20T06:26:27.736Z</v>
+      </c>
+      <c r="B45">
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-03-20T06:27:23.968Z</v>
+      </c>
+      <c r="B46">
+        <v>26</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>20</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-03-20T07:08:31.526Z</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F47"/>
   </ignoredErrors>
 </worksheet>
 </file>